--- a/artfynd/A 29855-2026 artfynd.xlsx
+++ b/artfynd/A 29855-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048244</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048292</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048237</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048308</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048246</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048391</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048393</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048396</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048398</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048403</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048336</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048216</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048218</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048220</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048222</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048224</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048248</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048250</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048259</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048261</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048272</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048274</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048277</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048279</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048281</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048284</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048286</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048288</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048290</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048294</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048298</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048303</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048305</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048310</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048313</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048323</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048326</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4738,6 +4928,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048330</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4845,6 +5040,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048338</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4952,6 +5152,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048340</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5059,6 +5264,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048351</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048355</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5273,6 +5488,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048357</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5380,6 +5600,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048358</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5487,6 +5712,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048360</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5594,6 +5824,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048363</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5701,6 +5936,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048365</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5808,6 +6048,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048367</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5915,6 +6160,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048369</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6022,6 +6272,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048371</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6129,6 +6384,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048373</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6236,6 +6496,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048375</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6343,6 +6608,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048377</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6450,6 +6720,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048378</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6557,6 +6832,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048380</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6664,6 +6944,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048382</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6771,6 +7056,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048384</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6878,6 +7168,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048399</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6985,6 +7280,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048400</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7092,6 +7392,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048401</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7199,6 +7504,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048406</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7306,6 +7616,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048270</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7413,6 +7728,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048226</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7520,6 +7840,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048296</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7627,6 +7952,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048315</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7734,6 +8064,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048235</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7841,6 +8176,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048242</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7948,6 +8288,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048252</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8055,6 +8400,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048257</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8162,6 +8512,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048334</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8269,6 +8624,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048228</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8376,6 +8736,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048233</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8483,6 +8848,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048240</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8590,6 +8960,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048254</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8697,6 +9072,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048328</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8804,6 +9184,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048353</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8911,6 +9296,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048321</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9018,6 +9408,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048394</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9125,6 +9520,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048395</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9232,6 +9632,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048397</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9339,6 +9744,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048402</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9446,6 +9856,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048386</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9553,6 +9968,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048404</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9670,6 +10090,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048347</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9777,6 +10202,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048230</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9884,6 +10314,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048264</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9991,8 +10426,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048332</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29855-2026 artfynd.xlsx
+++ b/artfynd/A 29855-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135048244</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135048292</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135048237</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135048308</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135048246</v>
       </c>
       <c r="B6" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135048391</v>
       </c>
       <c r="B7" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135048393</v>
       </c>
       <c r="B8" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135048396</v>
       </c>
       <c r="B9" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135048398</v>
       </c>
       <c r="B10" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135048403</v>
       </c>
       <c r="B11" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135048336</v>
       </c>
       <c r="B12" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135048216</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135048218</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135048220</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135048222</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135048224</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135048248</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135048250</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135048259</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135048261</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135048272</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135048274</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135048277</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135048279</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135048281</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135048284</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135048286</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135048288</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135048290</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135048294</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135048298</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135048303</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135048305</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135048310</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135048313</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135048323</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135048326</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135048330</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135048338</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135048340</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135048351</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>135048355</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>135048357</v>
       </c>
       <c r="B44" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>135048358</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>135048360</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>135048363</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>135048365</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>135048367</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>135048369</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>135048371</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>135048373</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>135048375</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>135048377</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135048378</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>135048380</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>135048382</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>135048384</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>135048399</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>135048400</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135048401</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>135048406</v>
       </c>
       <c r="B62" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>135048270</v>
       </c>
       <c r="B63" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>135048226</v>
       </c>
       <c r="B64" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>135048296</v>
       </c>
       <c r="B65" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>135048315</v>
       </c>
       <c r="B66" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>135048235</v>
       </c>
       <c r="B67" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>135048242</v>
       </c>
       <c r="B68" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>135048252</v>
       </c>
       <c r="B69" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>135048257</v>
       </c>
       <c r="B70" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>135048334</v>
       </c>
       <c r="B71" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>135048228</v>
       </c>
       <c r="B72" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>135048233</v>
       </c>
       <c r="B73" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>135048240</v>
       </c>
       <c r="B74" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135048254</v>
       </c>
       <c r="B75" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>135048328</v>
       </c>
       <c r="B76" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>135048353</v>
       </c>
       <c r="B77" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>135048321</v>
       </c>
       <c r="B78" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>135048394</v>
       </c>
       <c r="B79" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>135048395</v>
       </c>
       <c r="B80" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>135048397</v>
       </c>
       <c r="B81" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>135048402</v>
       </c>
       <c r="B82" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>135048386</v>
       </c>
       <c r="B83" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135048404</v>
       </c>
       <c r="B84" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>135048347</v>
       </c>
       <c r="B85" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>135048230</v>
       </c>
       <c r="B86" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>135048264</v>
       </c>
       <c r="B87" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>135048332</v>
       </c>
       <c r="B88" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 29855-2026 artfynd.xlsx
+++ b/artfynd/A 29855-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135048244</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135048292</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135048237</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135048308</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135048246</v>
       </c>
       <c r="B6" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135048391</v>
       </c>
       <c r="B7" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135048393</v>
       </c>
       <c r="B8" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135048396</v>
       </c>
       <c r="B9" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135048398</v>
       </c>
       <c r="B10" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135048403</v>
       </c>
       <c r="B11" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135048336</v>
       </c>
       <c r="B12" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135048216</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135048218</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135048220</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135048222</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135048224</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135048248</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135048250</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135048259</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135048261</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135048272</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135048274</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135048277</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135048279</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135048281</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135048284</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135048286</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135048288</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135048290</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135048294</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135048298</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135048303</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135048305</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135048310</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135048313</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135048323</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135048326</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135048330</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135048338</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135048340</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135048351</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>135048355</v>
       </c>
       <c r="B43" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>135048357</v>
       </c>
       <c r="B44" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>135048358</v>
       </c>
       <c r="B45" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>135048360</v>
       </c>
       <c r="B46" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>135048363</v>
       </c>
       <c r="B47" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>135048365</v>
       </c>
       <c r="B48" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>135048367</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>135048369</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>135048371</v>
       </c>
       <c r="B51" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>135048373</v>
       </c>
       <c r="B52" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>135048375</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>135048377</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135048378</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>135048380</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>135048382</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>135048384</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>135048399</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>135048400</v>
       </c>
       <c r="B60" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135048401</v>
       </c>
       <c r="B61" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>135048406</v>
       </c>
       <c r="B62" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>135048270</v>
       </c>
       <c r="B63" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>135048226</v>
       </c>
       <c r="B64" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>135048296</v>
       </c>
       <c r="B65" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>135048315</v>
       </c>
       <c r="B66" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>135048235</v>
       </c>
       <c r="B67" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>135048242</v>
       </c>
       <c r="B68" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>135048252</v>
       </c>
       <c r="B69" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>135048257</v>
       </c>
       <c r="B70" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>135048334</v>
       </c>
       <c r="B71" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>135048228</v>
       </c>
       <c r="B72" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>135048233</v>
       </c>
       <c r="B73" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>135048240</v>
       </c>
       <c r="B74" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135048254</v>
       </c>
       <c r="B75" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>135048328</v>
       </c>
       <c r="B76" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>135048353</v>
       </c>
       <c r="B77" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>135048321</v>
       </c>
       <c r="B78" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>135048394</v>
       </c>
       <c r="B79" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>135048395</v>
       </c>
       <c r="B80" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>135048397</v>
       </c>
       <c r="B81" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>135048402</v>
       </c>
       <c r="B82" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>135048386</v>
       </c>
       <c r="B83" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135048404</v>
       </c>
       <c r="B84" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>135048230</v>
       </c>
       <c r="B86" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>135048264</v>
       </c>
       <c r="B87" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>135048332</v>
       </c>
       <c r="B88" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
